--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\str\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E409DE6A-3596-4206-A442-947D39BDB17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543556C7-DB93-409A-8B82-BF0F639CF9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3828" yWindow="5676" windowWidth="12936" windowHeight="10176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/products.xlsx
+++ b/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\str\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543556C7-DB93-409A-8B82-BF0F639CF9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A821FE18-20B4-46C9-B33B-216988A18076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3828" yWindow="5676" windowWidth="12936" windowHeight="10176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="78">
   <si>
     <t>category_id</t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t>44мм</t>
-  </si>
-  <si>
-    <t>Apple Watch SE</t>
   </si>
   <si>
     <t>40мм</t>
@@ -1172,7 +1169,7 @@
         <v>31</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1195,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1255,13 +1252,13 @@
         <v>28</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" s="1">
         <v>5500</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>8</v>
@@ -1327,13 +1324,13 @@
         <v>49</v>
       </c>
       <c r="E32" s="1">
-        <v>39000</v>
+        <v>20000</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1350,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="E33" s="1">
-        <v>22500</v>
+        <v>15500</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>51</v>
@@ -1373,7 +1370,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="1">
-        <v>22000</v>
+        <v>22500</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>54</v>
@@ -1393,13 +1390,13 @@
         <v>34</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="E35" s="1">
-        <v>34600</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>8</v>
@@ -1416,13 +1413,13 @@
         <v>35</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" s="1">
         <v>10000</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>8</v>
@@ -1439,13 +1436,13 @@
         <v>36</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E37" s="1">
         <v>12000</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>8</v>
@@ -1462,13 +1459,13 @@
         <v>37</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E38" s="1">
         <v>31000</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>8</v>
@@ -1485,13 +1482,13 @@
         <v>38</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" s="1">
         <v>15000</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>8</v>
@@ -1508,13 +1505,13 @@
         <v>39</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" s="1">
         <v>19000</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>8</v>
@@ -1531,13 +1528,13 @@
         <v>40</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E41" s="1">
         <v>61000</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>8</v>
@@ -1554,13 +1551,13 @@
         <v>41</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E42" s="1">
         <v>101000</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>8</v>
@@ -1577,13 +1574,13 @@
         <v>42</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E43" s="1">
         <v>85000</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>8</v>
@@ -1600,13 +1597,13 @@
         <v>43</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44" s="1">
         <v>79000</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>8</v>
@@ -1623,13 +1620,13 @@
         <v>44</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E45" s="1">
         <v>107000</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>8</v>
@@ -1646,13 +1643,13 @@
         <v>45</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46" s="1">
         <v>90000</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>8</v>
@@ -1669,13 +1666,13 @@
         <v>46</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E47" s="1">
         <v>100000</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>8</v>
@@ -1692,13 +1689,13 @@
         <v>47</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E48" s="1">
         <v>110000</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>8</v>
@@ -1715,13 +1712,13 @@
         <v>48</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E49" s="1">
         <v>150000</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>8</v>
@@ -1738,13 +1735,13 @@
         <v>49</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50" s="1">
         <v>40000</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>8</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\str\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A821FE18-20B4-46C9-B33B-216988A18076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB08A430-214F-4F8B-81D7-16A0D2B254FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1278,7 +1278,7 @@
         <v>48</v>
       </c>
       <c r="E30" s="1">
-        <v>101000</v>
+        <v>67000</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>47</v>
@@ -1301,7 +1301,7 @@
         <v>52</v>
       </c>
       <c r="E31" s="1">
-        <v>91000</v>
+        <v>60000</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>47</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\str\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB08A430-214F-4F8B-81D7-16A0D2B254FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C305FB7-A5CF-4C0D-ADE0-698D2B0E8593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="83">
   <si>
     <t>category_id</t>
   </si>
@@ -259,6 +259,21 @@
   </si>
   <si>
     <t xml:space="preserve"> Sony PlayStation DualSense</t>
+  </si>
+  <si>
+    <t>dyson</t>
+  </si>
+  <si>
+    <t>Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фен-выпрямитель Dyson HT01 </t>
+  </si>
+  <si>
+    <t>Вертикальный пылеcoс Dysоn V15s</t>
+  </si>
+  <si>
+    <t>Стайлер Dyson HS09 Airwrap Co-anda 2x</t>
   </si>
 </sst>
 </file>
@@ -585,13 +600,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="1"/>
     <col min="6" max="6" width="39.21875" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="1"/>
@@ -634,7 +649,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="1">
-        <v>33500</v>
+        <v>34500</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>13</v>
@@ -657,7 +672,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="1">
-        <v>37000</v>
+        <v>38000</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>14</v>
@@ -686,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -703,7 +718,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>43500</v>
+        <v>44500</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>14</v>
@@ -726,7 +741,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="1">
-        <v>50000</v>
+        <v>53000</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>14</v>
@@ -818,7 +833,7 @@
         <v>18</v>
       </c>
       <c r="E10" s="1">
-        <v>48000</v>
+        <v>49500</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>14</v>
@@ -841,7 +856,7 @@
         <v>19</v>
       </c>
       <c r="E11" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
@@ -864,7 +879,7 @@
         <v>19</v>
       </c>
       <c r="E12" s="1">
-        <v>95500</v>
+        <v>97500</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
@@ -910,7 +925,7 @@
         <v>19</v>
       </c>
       <c r="E14" s="1">
-        <v>141500</v>
+        <v>145500</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>20</v>
@@ -933,7 +948,7 @@
         <v>21</v>
       </c>
       <c r="E15" s="1">
-        <v>60500</v>
+        <v>59500</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>22</v>
@@ -979,7 +994,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1">
-        <v>44000</v>
+        <v>43500</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>24</v>
@@ -1094,7 +1109,7 @@
         <v>28</v>
       </c>
       <c r="E22" s="1">
-        <v>33500</v>
+        <v>31500</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>23</v>
@@ -1117,7 +1132,7 @@
         <v>28</v>
       </c>
       <c r="E23" s="1">
-        <v>30500</v>
+        <v>28500</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>24</v>
@@ -1209,7 +1224,7 @@
         <v>36</v>
       </c>
       <c r="E27" s="1">
-        <v>25000</v>
+        <v>26500</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>37</v>
@@ -1232,7 +1247,7 @@
         <v>38</v>
       </c>
       <c r="E28" s="1">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>16</v>
@@ -1278,7 +1293,7 @@
         <v>48</v>
       </c>
       <c r="E30" s="1">
-        <v>67000</v>
+        <v>63000</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>47</v>
@@ -1301,7 +1316,7 @@
         <v>52</v>
       </c>
       <c r="E31" s="1">
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>47</v>
@@ -1324,7 +1339,7 @@
         <v>49</v>
       </c>
       <c r="E32" s="1">
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>50</v>
@@ -1347,7 +1362,7 @@
         <v>49</v>
       </c>
       <c r="E33" s="1">
-        <v>15500</v>
+        <v>18500</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>51</v>
@@ -1370,7 +1385,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="1">
-        <v>22500</v>
+        <v>24500</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>54</v>
@@ -1393,7 +1408,7 @@
         <v>53</v>
       </c>
       <c r="E35" s="1">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>55</v>
@@ -1508,7 +1523,7 @@
         <v>61</v>
       </c>
       <c r="E40" s="1">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>57</v>
@@ -1600,7 +1615,7 @@
         <v>63</v>
       </c>
       <c r="E44" s="1">
-        <v>79000</v>
+        <v>74000</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>74</v>
@@ -1623,7 +1638,7 @@
         <v>63</v>
       </c>
       <c r="E45" s="1">
-        <v>107000</v>
+        <v>100000</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>72</v>
@@ -1669,7 +1684,7 @@
         <v>67</v>
       </c>
       <c r="E47" s="1">
-        <v>100000</v>
+        <v>95000</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>68</v>
@@ -1738,12 +1753,81 @@
         <v>64</v>
       </c>
       <c r="E50" s="1">
-        <v>40000</v>
+        <v>39500</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>65</v>
       </c>
       <c r="G50" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="1">
+        <v>50</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" s="1">
+        <v>24500</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52" s="1">
+        <v>51</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" s="1">
+        <v>44000</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="1">
+        <v>52</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="1">
+        <v>41000</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\str\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C305FB7-A5CF-4C0D-ADE0-698D2B0E8593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66268292-59B0-4480-A34D-0C15F1C6A1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1178,13 +1178,13 @@
         <v>30</v>
       </c>
       <c r="E25" s="1">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1207,7 +1207,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
